--- a/5/search/FY3_Missile3_results/fine_tuned/original_top5_solutions.xlsx
+++ b/5/search/FY3_Missile3_results/fine_tuned/original_top5_solutions.xlsx
@@ -490,28 +490,28 @@
         <v>81</v>
       </c>
       <c r="B2" t="n">
-        <v>120.4</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6452.033030180251</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="I2" t="n">
-        <v>-145.9757710162899</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="J2" t="n">
         <v>700</v>
@@ -525,139 +525,139 @@
         <v>81</v>
       </c>
       <c r="B3" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6420.495842028141</v>
+        <v>6431.759123511038</v>
       </c>
       <c r="F3" t="n">
-        <v>-345.0937404802698</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6446.7768321549</v>
+        <v>6453.347079686589</v>
       </c>
       <c r="I3" t="n">
-        <v>-179.1620992602867</v>
+        <v>-137.6791889552907</v>
       </c>
       <c r="J3" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B4" t="n">
-        <v>128.8</v>
+        <v>136</v>
       </c>
       <c r="C4" t="n">
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>6000</v>
+        <v>6213.408740379738</v>
       </c>
       <c r="F4" t="n">
-        <v>-424</v>
+        <v>-288.384852245892</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6000</v>
+        <v>6224.079177398726</v>
       </c>
       <c r="I4" t="n">
-        <v>-166.4</v>
+        <v>-152.8040948581866</v>
       </c>
       <c r="J4" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126</v>
+        <v>112.5</v>
       </c>
       <c r="B5" t="n">
-        <v>114.8</v>
+        <v>122</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>4380.534072883778</v>
+        <v>5066.252425029181</v>
       </c>
       <c r="F5" t="n">
-        <v>-770.9963770981449</v>
+        <v>-745.7339406724604</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>3908.189844141547</v>
+        <v>4786.128152537935</v>
       </c>
       <c r="I5" t="n">
-        <v>-120.8703204184371</v>
+        <v>-69.45412287419856</v>
       </c>
       <c r="J5" t="n">
-        <v>459.9</v>
+        <v>523.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126</v>
+        <v>94.5</v>
       </c>
       <c r="B6" t="n">
-        <v>134.4</v>
+        <v>124</v>
       </c>
       <c r="C6" t="n">
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>4420.033241837833</v>
+        <v>5805.421442594945</v>
       </c>
       <c r="F6" t="n">
-        <v>-825.3623191201414</v>
+        <v>-527.6450123418426</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>3867.044876481074</v>
+        <v>5776.234658984186</v>
       </c>
       <c r="I6" t="n">
-        <v>-64.23913081219098</v>
+        <v>-156.791764193119</v>
       </c>
       <c r="J6" t="n">
-        <v>459.9</v>
+        <v>655.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
